--- a/data/trans_dic/P12_1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P12_1_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se sintió calmada y tranquila alguna vez o algunas veces</t>
+          <t>Población que se sintió calmada y tranquila alguna vez o algunas veces (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,93; 25,38</t>
+          <t>20,13; 25,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,1; 21,27</t>
+          <t>16,25; 21,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,32; 21,85</t>
+          <t>16,31; 22,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,1; 21,51</t>
+          <t>15,09; 21,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,84; 28,77</t>
+          <t>23,82; 28,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,07; 34,42</t>
+          <t>28,92; 34,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,48; 28,41</t>
+          <t>22,22; 28,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,86; 28,75</t>
+          <t>23,81; 28,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,9; 26,43</t>
+          <t>22,84; 26,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24,23; 27,94</t>
+          <t>24,44; 28,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,54; 24,44</t>
+          <t>20,68; 24,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,98; 24,82</t>
+          <t>20,86; 24,72</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,58; 16,15</t>
+          <t>12,59; 16,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,39; 16,65</t>
+          <t>13,47; 16,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,32; 11,02</t>
+          <t>8,41; 10,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,64; 13,17</t>
+          <t>7,55; 13,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,05; 22,16</t>
+          <t>18,06; 22,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,85; 26,18</t>
+          <t>21,85; 26,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,79; 14,82</t>
+          <t>11,69; 14,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,17; 46,25</t>
+          <t>16,1; 42,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,9; 18,44</t>
+          <t>15,75; 18,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,94; 20,53</t>
+          <t>17,88; 20,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,44; 12,37</t>
+          <t>10,34; 12,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,29; 30,28</t>
+          <t>13,25; 30,31</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,58; 17,97</t>
+          <t>11,92; 18,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,13; 16,99</t>
+          <t>10,04; 16,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,73; 11,89</t>
+          <t>6,65; 12,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,48; 16,07</t>
+          <t>10,41; 15,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,57; 23,2</t>
+          <t>15,66; 23,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,08; 20,13</t>
+          <t>13,23; 20,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,99; 17,25</t>
+          <t>10,99; 16,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,92; 20,14</t>
+          <t>15,11; 20,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,6; 19,42</t>
+          <t>14,46; 19,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,29; 17,38</t>
+          <t>12,46; 17,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,59; 13,64</t>
+          <t>9,66; 13,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,33; 17,15</t>
+          <t>13,68; 17,26</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,61; 18,21</t>
+          <t>15,67; 18,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,36; 17,06</t>
+          <t>14,45; 17,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,56; 12,98</t>
+          <t>10,5; 12,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,66; 14,16</t>
+          <t>9,57; 14,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,9; 23,79</t>
+          <t>21,05; 23,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,35; 27,4</t>
+          <t>24,3; 27,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,5; 17,93</t>
+          <t>15,26; 17,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,46; 39,91</t>
+          <t>18,47; 37,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,66; 20,82</t>
+          <t>18,77; 20,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,89; 21,89</t>
+          <t>20,01; 21,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,33; 15,08</t>
+          <t>13,38; 15,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,38; 28,28</t>
+          <t>15,14; 27,28</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se sintió calmada y tranquila alguna vez o algunas veces</t>
+          <t>Población que se sintió calmada y tranquila alguna vez o algunas veces (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>205666; 261871</t>
+          <t>207698; 262495</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>156558; 206852</t>
+          <t>158047; 207397</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>123084; 164800</t>
+          <t>123038; 166177</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77649; 110599</t>
+          <t>77602; 109089</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>313505; 378395</t>
+          <t>313246; 375798</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>388266; 459818</t>
+          <t>386360; 459623</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>223148; 282011</t>
+          <t>220565; 278479</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>180297; 217188</t>
+          <t>179855; 216080</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>537435; 620315</t>
+          <t>535909; 620780</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>559365; 644873</t>
+          <t>564084; 653358</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>358805; 426931</t>
+          <t>361236; 429477</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>266333; 315107</t>
+          <t>264868; 313843</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>213025; 273478</t>
+          <t>213277; 271034</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>262743; 326811</t>
+          <t>264348; 330265</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>172534; 228535</t>
+          <t>174356; 227874</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>174964; 301615</t>
+          <t>173020; 302896</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>286501; 351901</t>
+          <t>286806; 351275</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>382985; 458970</t>
+          <t>383082; 457073</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>234167; 294390</t>
+          <t>232210; 292109</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>361772; 1034457</t>
+          <t>360046; 961338</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>521777; 604993</t>
+          <t>516622; 605838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>666550; 762987</t>
+          <t>664180; 762744</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>423773; 502226</t>
+          <t>419913; 500862</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>601753; 1370885</t>
+          <t>599628; 1372067</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>63827; 99071</t>
+          <t>65745; 100401</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48757; 81751</t>
+          <t>48304; 81248</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36789; 65011</t>
+          <t>36347; 66437</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67751; 103943</t>
+          <t>67340; 103248</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>74190; 110524</t>
+          <t>74596; 110406</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>59829; 92105</t>
+          <t>60536; 92416</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60113; 94383</t>
+          <t>60153; 91919</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>98540; 133007</t>
+          <t>99803; 133538</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>150092; 199602</t>
+          <t>148574; 200223</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>115398; 163120</t>
+          <t>116936; 163958</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>104904; 149219</t>
+          <t>105708; 146568</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>174273; 224105</t>
+          <t>178753; 225569</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>511610; 596679</t>
+          <t>513326; 598104</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>490764; 582790</t>
+          <t>493636; 586377</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>356391; 437972</t>
+          <t>354273; 431411</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>333204; 488515</t>
+          <t>330261; 486960</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>706186; 803807</t>
+          <t>711226; 805335</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>863393; 971751</t>
+          <t>861780; 978560</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>546596; 632056</t>
+          <t>537930; 633013</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>674126; 1457810</t>
+          <t>674557; 1385794</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1242138; 1385570</t>
+          <t>1249092; 1376110</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1384824; 1524041</t>
+          <t>1393479; 1527315</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>920106; 1040756</t>
+          <t>923284; 1036869</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1092367; 2008841</t>
+          <t>1075517; 1938079</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P12_1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P12_1_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,13; 25,44</t>
+          <t>20,12; 25,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,25; 21,32</t>
+          <t>16,14; 21,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,31; 22,03</t>
+          <t>16,21; 21,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,09; 21,22</t>
+          <t>14,32; 20,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,82; 28,58</t>
+          <t>23,77; 28,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,92; 34,41</t>
+          <t>28,93; 34,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,22; 28,06</t>
+          <t>22,38; 28,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,81; 28,6</t>
+          <t>24,04; 28,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,84; 26,45</t>
+          <t>22,83; 26,34</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24,44; 28,3</t>
+          <t>24,34; 28,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,68; 24,59</t>
+          <t>20,36; 24,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,86; 24,72</t>
+          <t>20,65; 24,6</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,59; 16,01</t>
+          <t>12,69; 15,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,47; 16,83</t>
+          <t>13,25; 16,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,41; 10,99</t>
+          <t>8,34; 10,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 13,23</t>
+          <t>11,02; 14,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,06; 22,13</t>
+          <t>18,26; 22,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,85; 26,08</t>
+          <t>21,76; 25,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,69; 14,71</t>
+          <t>11,68; 14,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,1; 42,98</t>
+          <t>16,18; 19,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,75; 18,46</t>
+          <t>15,86; 18,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,88; 20,53</t>
+          <t>17,96; 20,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,34; 12,34</t>
+          <t>10,4; 12,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,25; 30,31</t>
+          <t>13,99; 16,1</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,92; 18,21</t>
+          <t>12,04; 17,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,04; 16,89</t>
+          <t>9,86; 16,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,65; 12,15</t>
+          <t>6,8; 11,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,41; 15,97</t>
+          <t>10,97; 16,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,66; 23,17</t>
+          <t>15,9; 23,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,23; 20,2</t>
+          <t>12,99; 20,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,99; 16,8</t>
+          <t>10,86; 17,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,11; 20,22</t>
+          <t>15,37; 20,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,46; 19,48</t>
+          <t>14,6; 19,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,46; 17,47</t>
+          <t>12,2; 17,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,66; 13,4</t>
+          <t>9,57; 13,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,68; 17,26</t>
+          <t>13,88; 17,43</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,67; 18,25</t>
+          <t>15,64; 18,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,45; 17,16</t>
+          <t>14,5; 17,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,5; 12,78</t>
+          <t>10,56; 12,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,57; 14,11</t>
+          <t>12,36; 14,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,05; 23,83</t>
+          <t>21,04; 23,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,3; 27,59</t>
+          <t>24,34; 27,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,26; 17,95</t>
+          <t>15,47; 17,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,47; 37,94</t>
+          <t>18,43; 20,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,77; 20,68</t>
+          <t>18,66; 20,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,01; 21,94</t>
+          <t>19,97; 21,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,38; 15,02</t>
+          <t>13,3; 15,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,14; 27,28</t>
+          <t>15,76; 17,32</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91938</t>
+          <t>98541</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>197633</t>
+          <t>216664</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>289570</t>
+          <t>315205</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>207698; 262495</t>
+          <t>207554; 260178</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>158047; 207397</t>
+          <t>157002; 205964</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>123038; 166177</t>
+          <t>122271; 163282</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77602; 109089</t>
+          <t>82721; 116128</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>313246; 375798</t>
+          <t>312623; 377161</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>386360; 459623</t>
+          <t>386454; 455246</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>220565; 278479</t>
+          <t>222108; 279518</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>179855; 216080</t>
+          <t>197635; 235348</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>535909; 620780</t>
+          <t>535809; 618243</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>564084; 653358</t>
+          <t>561945; 651830</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>361236; 429477</t>
+          <t>355732; 427204</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>264868; 313843</t>
+          <t>289073; 344293</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>257004</t>
+          <t>276149</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>544996</t>
+          <t>380728</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>802000</t>
+          <t>656877</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>213277; 271034</t>
+          <t>214909; 270182</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>264348; 330265</t>
+          <t>260132; 326545</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>174356; 227874</t>
+          <t>172891; 227016</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>173020; 302896</t>
+          <t>245842; 315462</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>286806; 351275</t>
+          <t>289852; 357100</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>383082; 457073</t>
+          <t>381420; 455044</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>232210; 292109</t>
+          <t>231896; 295752</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>360046; 961338</t>
+          <t>351262; 413255</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516622; 605838</t>
+          <t>520222; 608448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>664180; 762744</t>
+          <t>667459; 774151</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>419913; 500862</t>
+          <t>422377; 500605</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>599628; 1372067</t>
+          <t>615700; 708388</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84869</t>
+          <t>96111</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>115239</t>
+          <t>129477</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>200107</t>
+          <t>225588</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>65745; 100401</t>
+          <t>66402; 98792</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48304; 81248</t>
+          <t>47433; 80738</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36347; 66437</t>
+          <t>37183; 65438</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67340; 103248</t>
+          <t>78030; 115050</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>74596; 110406</t>
+          <t>75756; 110563</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60536; 92416</t>
+          <t>59431; 93472</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60153; 91919</t>
+          <t>59448; 93602</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>99803; 133538</t>
+          <t>112956; 147707</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>148574; 200223</t>
+          <t>150039; 200927</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>116936; 163958</t>
+          <t>114543; 161084</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>105708; 146568</t>
+          <t>104732; 148110</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>178753; 225569</t>
+          <t>200735; 252118</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>433811</t>
+          <t>470800</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>857867</t>
+          <t>726870</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1291678</t>
+          <t>1197670</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>513326; 598104</t>
+          <t>512557; 598780</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>493636; 586377</t>
+          <t>495554; 585050</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>354273; 431411</t>
+          <t>356483; 432064</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>330261; 486960</t>
+          <t>434933; 514603</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>711226; 805335</t>
+          <t>710915; 807951</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>861780; 978560</t>
+          <t>863178; 970635</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>537930; 633013</t>
+          <t>545447; 633155</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>674557; 1385794</t>
+          <t>686888; 770972</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1249092; 1376110</t>
+          <t>1241836; 1377343</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1393479; 1527315</t>
+          <t>1390732; 1524581</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>923284; 1036869</t>
+          <t>917707; 1040366</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1075517; 1938079</t>
+          <t>1142032; 1255181</t>
         </is>
       </c>
     </row>
